--- a/output_plant/stomata_Intermediate_stults_2011.xlsx
+++ b/output_plant/stomata_Intermediate_stults_2011.xlsx
@@ -606,7 +606,7 @@
     <t xml:space="preserve">10.1016/j.palaeo.2011.06.017</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-sd_stults_2011.xlsx</t>
+    <t xml:space="preserve">stomata-sd_stults_2011_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>

--- a/output_plant/stomata_Intermediate_stults_2011.xlsx
+++ b/output_plant/stomata_Intermediate_stults_2011.xlsx
@@ -615,7 +615,7 @@
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">biostratigraphy: late Miocene (probably Tortonian-Messinian, based on published age of 11.2-6.5 Ma)</t>
+    <t xml:space="preserve">biostratigraphy: late Miocene (probably Tortonian-Messinian, based on published age of 11.2-6.5 Ma); Biostratigraphy updated to GTS2020</t>
   </si>
   <si>
     <t xml:space="preserve">Cuppressaceae / Taxodium</t>
@@ -633,7 +633,7 @@
     <t xml:space="preserve">Stomatal density treated as abaxial; density and uncertainty converted from mm^-2 to m^-2.</t>
   </si>
   <si>
-    <t xml:space="preserve">biostratigraphy: Pliocene (probably Piacenzian, based on published age of 3.4-2.7 Ma)</t>
+    <t xml:space="preserve">biostratigraphy: Pliocene (probably Piacenzian, based on published age of 3.4-2.7 Ma); Biostratigraphy updated to GTS2020</t>
   </si>
 </sst>
 </file>
@@ -2049,14 +2049,14 @@
         <v>-87.485333</v>
       </c>
       <c r="H6" s="23" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="23" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="K6" s="23" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>206</v>
